--- a/Result/profitability/2059.xlsx
+++ b/Result/profitability/2059.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.27</v>
       </c>
       <c r="M2" t="n">
-        <v>22.10375</v>
+        <v>29.88625</v>
       </c>
       <c r="N2" t="n">
-        <v>71.84125</v>
+        <v>73.95125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>2.79</v>
       </c>
       <c r="M3" t="n">
-        <v>20.9375</v>
+        <v>27.405</v>
       </c>
       <c r="N3" t="n">
-        <v>68.99625</v>
+        <v>70.94749999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>3.02</v>
       </c>
       <c r="M4" t="n">
-        <v>18.485</v>
+        <v>24.48875</v>
       </c>
       <c r="N4" t="n">
-        <v>65.68124999999999</v>
+        <v>67.10250000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>15.46625</v>
+        <v>23.95875</v>
       </c>
       <c r="N5" t="n">
-        <v>62.5175</v>
+        <v>63.7575</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.69</v>
       </c>
       <c r="M6" t="n">
-        <v>14.8725</v>
+        <v>19.97625</v>
       </c>
       <c r="N6" t="n">
-        <v>58.7075</v>
+        <v>60.3125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.44</v>
       </c>
       <c r="M7" t="n">
-        <v>10.85875</v>
+        <v>15.54625</v>
       </c>
       <c r="N7" t="n">
-        <v>55.2125</v>
+        <v>56.6275</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>6.58</v>
+        <v>11.305</v>
       </c>
       <c r="N8" t="n">
-        <v>52.30125</v>
+        <v>53.51125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>1.96125</v>
       </c>
       <c r="N13" t="n">
-        <v>51.52374999999999</v>
+        <v>51.52375</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>10830</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1362</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9468</v>
+      </c>
+      <c r="F75" t="n">
+        <v>87.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>8890</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>82.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>229</v>
+      </c>
+      <c r="J75" t="n">
+        <v>9118</v>
+      </c>
+      <c r="K75" t="n">
+        <v>7088</v>
+      </c>
+      <c r="L75" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>31.1175</v>
+      </c>
+      <c r="N75" t="n">
+        <v>76.4675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.03335155822854</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>9.680000000000007</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1245176228453821</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>67.94</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>10.54968944099379</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9.920000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1280000000000001</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
